--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2025/A320_Airline_Cumulative_Statistics_2025.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2025/A320_Airline_Cumulative_Statistics_2025.xlsx
@@ -13,42 +13,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="21" uniqueCount="21">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>A319</t>
-  </si>
-  <si>
-    <t>A320</t>
-  </si>
-  <si>
-    <t>A321</t>
-  </si>
-  <si>
-    <t>A321NEO</t>
-  </si>
-  <si>
-    <t>B737-800</t>
-  </si>
-  <si>
-    <t>B737-8</t>
-  </si>
-  <si>
-    <t>B787-8</t>
-  </si>
-  <si>
-    <t>B787-9</t>
-  </si>
-  <si>
-    <t>B777-200</t>
-  </si>
-  <si>
-    <t>B777-300</t>
-  </si>
-  <si>
-    <t>All Aircraft</t>
+    <t>Allegiant</t>
+  </si>
+  <si>
+    <t>American</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>Frontier</t>
+  </si>
+  <si>
+    <t>JetBlue</t>
+  </si>
+  <si>
+    <t>Spirit</t>
+  </si>
+  <si>
+    <t>United</t>
+  </si>
+  <si>
+    <t>All Airlines</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -130,10 +121,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="true"/>
+    <col min="1" max="1" width="9.5703125" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -153,40 +144,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="F1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="G1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="H1" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="I1" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="J1" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="K1" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="L1" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="M1" s="0" t="s">
         <v>20</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -194,40 +185,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>13442500816</v>
+        <v>11919261764</v>
       </c>
       <c r="C2" s="0">
-        <v>16599243784</v>
+        <v>14399030838</v>
       </c>
       <c r="D2" s="0">
-        <v>343101</v>
+        <v>471172</v>
       </c>
       <c r="E2" s="0">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="F2" s="0">
-        <v>195486</v>
+        <v>84532</v>
       </c>
       <c r="G2" s="0">
-        <v>4.04</v>
+        <v>2.77</v>
       </c>
       <c r="H2" s="0">
-        <v>8.3200000000000003</v>
+        <v>6.9199999999999999</v>
       </c>
       <c r="I2" s="0">
-        <v>80.980000000000004</v>
+        <v>82.780000000000001</v>
       </c>
       <c r="J2" s="0">
-        <v>663</v>
+        <v>945</v>
       </c>
       <c r="K2" s="0">
-        <v>4398</v>
+        <v>5064.6700000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>34.359999999999999</v>
+        <v>28.079999999999998</v>
       </c>
       <c r="M2" s="0">
-        <v>0.11</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="3">
@@ -262,13 +253,13 @@
         <v>721</v>
       </c>
       <c r="K3" s="0">
-        <v>5084</v>
+        <v>5084.3000000000002</v>
       </c>
       <c r="L3" s="0">
         <v>33.899999999999999</v>
       </c>
       <c r="M3" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -276,40 +267,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>46386063988</v>
+        <v>7728682504</v>
       </c>
       <c r="C4" s="0">
-        <v>54873709275</v>
+        <v>9615017047</v>
       </c>
       <c r="D4" s="0">
-        <v>690409</v>
+        <v>529753</v>
       </c>
       <c r="E4" s="0">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="F4" s="0">
-        <v>267451</v>
+        <v>75281</v>
       </c>
       <c r="G4" s="0">
-        <v>3.3700000000000001</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="H4" s="0">
-        <v>10.050000000000001</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="I4" s="0">
-        <v>84.530000000000001</v>
+        <v>80.379999999999995</v>
       </c>
       <c r="J4" s="0">
-        <v>1131</v>
+        <v>814</v>
       </c>
       <c r="K4" s="0">
-        <v>6532</v>
+        <v>5602.7200000000003</v>
       </c>
       <c r="L4" s="0">
-        <v>35.780000000000001</v>
+        <v>35.689999999999998</v>
       </c>
       <c r="M4" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -317,40 +308,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>24830456909</v>
+        <v>1000908228</v>
       </c>
       <c r="C5" s="0">
-        <v>28884288183</v>
+        <v>1228423698</v>
       </c>
       <c r="D5" s="0">
-        <v>941470</v>
+        <v>548403</v>
       </c>
       <c r="E5" s="0">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F5" s="0">
-        <v>89807</v>
+        <v>7697</v>
       </c>
       <c r="G5" s="0">
-        <v>2.9300000000000002</v>
+        <v>3.4399999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>11.539999999999999</v>
+        <v>8.6799999999999997</v>
       </c>
       <c r="I5" s="0">
-        <v>85.969999999999999</v>
+        <v>81.480000000000004</v>
       </c>
       <c r="J5" s="0">
-        <v>1645</v>
+        <v>867</v>
       </c>
       <c r="K5" s="0">
-        <v>7089</v>
+        <v>4340.5799999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>36.270000000000003</v>
+        <v>23.57</v>
       </c>
       <c r="M5" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="6">
@@ -358,40 +349,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>53070829110</v>
+        <v>22580328939</v>
       </c>
       <c r="C6" s="0">
-        <v>64299143283</v>
+        <v>27661693626</v>
       </c>
       <c r="D6" s="0">
-        <v>581314</v>
+        <v>585309</v>
       </c>
       <c r="E6" s="0">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F6" s="0">
-        <v>395193</v>
+        <v>153260</v>
       </c>
       <c r="G6" s="0">
-        <v>3.5699999999999998</v>
+        <v>3.2400000000000002</v>
       </c>
       <c r="H6" s="0">
-        <v>9.4600000000000009</v>
+        <v>9.6699999999999999</v>
       </c>
       <c r="I6" s="0">
-        <v>82.540000000000006</v>
+        <v>81.629999999999995</v>
       </c>
       <c r="J6" s="0">
-        <v>946</v>
+        <v>1119</v>
       </c>
       <c r="K6" s="0">
-        <v>5783</v>
+        <v>6231.6899999999996</v>
       </c>
       <c r="L6" s="0">
-        <v>33.619999999999997</v>
+        <v>38.649999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -399,40 +390,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>16894589044</v>
+        <v>8941025037</v>
       </c>
       <c r="C7" s="0">
-        <v>19975556880</v>
+        <v>11336340928</v>
       </c>
       <c r="D7" s="0">
-        <v>714945</v>
+        <v>488425</v>
       </c>
       <c r="E7" s="0">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F7" s="0">
-        <v>94496</v>
+        <v>72283</v>
       </c>
       <c r="G7" s="0">
-        <v>3.3799999999999999</v>
+        <v>3.1099999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>10.789999999999999</v>
+        <v>7.6600000000000001</v>
       </c>
       <c r="I7" s="0">
-        <v>84.579999999999998</v>
+        <v>78.870000000000005</v>
       </c>
       <c r="J7" s="0">
-        <v>1229</v>
+        <v>891</v>
       </c>
       <c r="K7" s="0">
-        <v>5832</v>
+        <v>5137.71</v>
       </c>
       <c r="L7" s="0">
-        <v>33.909999999999997</v>
+        <v>29.190000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="8">
@@ -440,40 +431,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>15572531550</v>
+        <v>8602245264</v>
       </c>
       <c r="C8" s="0">
-        <v>17832182422</v>
+        <v>10672248300</v>
       </c>
       <c r="D8" s="0">
-        <v>1320902</v>
+        <v>386816</v>
       </c>
       <c r="E8" s="0">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="F8" s="0">
-        <v>19059</v>
+        <v>85124</v>
       </c>
       <c r="G8" s="0">
-        <v>1.4099999999999999</v>
+        <v>3.0899999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>11.470000000000001</v>
+        <v>7.5099999999999998</v>
       </c>
       <c r="I8" s="0">
-        <v>87.329999999999998</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="J8" s="0">
-        <v>4001</v>
+        <v>836</v>
       </c>
       <c r="K8" s="0">
-        <v>10990</v>
+        <v>5711.1400000000003</v>
       </c>
       <c r="L8" s="0">
-        <v>47</v>
+        <v>38.07</v>
       </c>
       <c r="M8" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="9">
@@ -481,163 +472,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>13696499133</v>
+        <v>66911351659</v>
       </c>
       <c r="C9" s="0">
-        <v>16180469360</v>
+        <v>82401204498</v>
       </c>
       <c r="D9" s="0">
-        <v>1678472</v>
+        <v>494813</v>
       </c>
       <c r="E9" s="0">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="F9" s="0">
-        <v>12084</v>
+        <v>547446</v>
       </c>
       <c r="G9" s="0">
-        <v>1.25</v>
+        <v>3.29</v>
       </c>
       <c r="H9" s="0">
-        <v>12.23</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="I9" s="0">
-        <v>84.650000000000006</v>
+        <v>81.200000000000003</v>
       </c>
       <c r="J9" s="0">
-        <v>4812</v>
+        <v>922</v>
       </c>
       <c r="K9" s="0">
-        <v>12891</v>
+        <v>5611.25</v>
       </c>
       <c r="L9" s="0">
-        <v>46.329999999999998</v>
+        <v>34.439999999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>0.089999999999999997</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0">
-        <v>21816241096</v>
-      </c>
-      <c r="C10" s="0">
-        <v>25761640242</v>
-      </c>
-      <c r="D10" s="0">
-        <v>1499513</v>
-      </c>
-      <c r="E10" s="0">
-        <v>272</v>
-      </c>
-      <c r="F10" s="0">
-        <v>22767</v>
-      </c>
-      <c r="G10" s="0">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="H10" s="0">
-        <v>11.31</v>
-      </c>
-      <c r="I10" s="0">
-        <v>84.680000000000007</v>
-      </c>
-      <c r="J10" s="0">
-        <v>4161</v>
-      </c>
-      <c r="K10" s="0">
-        <v>13617</v>
-      </c>
-      <c r="L10" s="0">
-        <v>50.079999999999998</v>
-      </c>
-      <c r="M10" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="0">
-        <v>10516369977</v>
-      </c>
-      <c r="C11" s="0">
-        <v>12870450445</v>
-      </c>
-      <c r="D11" s="0">
-        <v>1758258</v>
-      </c>
-      <c r="E11" s="0">
-        <v>304</v>
-      </c>
-      <c r="F11" s="0">
-        <v>9625</v>
-      </c>
-      <c r="G11" s="0">
-        <v>1.3100000000000001</v>
-      </c>
-      <c r="H11" s="0">
-        <v>11.789999999999999</v>
-      </c>
-      <c r="I11" s="0">
-        <v>81.709999999999994</v>
-      </c>
-      <c r="J11" s="0">
-        <v>4399</v>
-      </c>
-      <c r="K11" s="0">
-        <v>15451</v>
-      </c>
-      <c r="L11" s="0">
-        <v>50.829999999999998</v>
-      </c>
-      <c r="M11" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="0">
-        <v>222364981546</v>
-      </c>
-      <c r="C12" s="0">
-        <v>264765133935</v>
-      </c>
-      <c r="D12" s="0">
-        <v>730891</v>
-      </c>
-      <c r="E12" s="0">
-        <v>173</v>
-      </c>
-      <c r="F12" s="0">
-        <v>1175237</v>
-      </c>
-      <c r="G12" s="0">
-        <v>3.2400000000000002</v>
-      </c>
-      <c r="H12" s="0">
-        <v>9.9499999999999993</v>
-      </c>
-      <c r="I12" s="0">
-        <v>83.989999999999995</v>
-      </c>
-      <c r="J12" s="0">
-        <v>1184</v>
-      </c>
-      <c r="K12" s="0">
-        <v>7008</v>
-      </c>
-      <c r="L12" s="0">
-        <v>37.780000000000001</v>
-      </c>
-      <c r="M12" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
   </sheetData>
